--- a/data/vannmiljo_catch_metadata.xlsx
+++ b/data/vannmiljo_catch_metadata.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T74"/>
+  <dimension ref="A1:T75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7390,6 +7390,100 @@
       </c>
       <c r="T74" t="n">
         <v>316.2700390134703</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>129705</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>002-129705</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Bjørkemoen</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>002-599-R</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Jeksla</t>
+        </is>
+      </c>
+      <c r="R75" t="n">
+        <v>284073.0069000004</v>
+      </c>
+      <c r="S75" t="n">
+        <v>6662831.6373</v>
+      </c>
+      <c r="T75" t="n">
+        <v>612.0674559062604</v>
       </c>
     </row>
   </sheetData>
